--- a/ModExcel/J局内属性效果选择.xlsx
+++ b/ModExcel/J局内属性效果选择.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\branch1.0.4.35613\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\SurvivorsData\trunk\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E800E9-062F-4EF7-B63F-C4900605F95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A827036-0778-4FC1-ACBF-D25B9F7AB737}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="局内属性随机表" sheetId="1" r:id="rId1"/>
@@ -21,20 +21,7 @@
     <sheet name="局内辅助技能随机表" sheetId="4" r:id="rId6"/>
     <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -116,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2778" uniqueCount="1641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2837" uniqueCount="1685">
   <si>
     <t>1白2蓝3紫4金5红</t>
   </si>
@@ -5332,6 +5319,155 @@
   </si>
   <si>
     <t>17,18</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>永恒诅咒</t>
+  </si>
+  <si>
+    <t>扩张恶言</t>
+  </si>
+  <si>
+    <t>简化仪式</t>
+  </si>
+  <si>
+    <t>鲜血操术</t>
+  </si>
+  <si>
+    <t>射手训练</t>
+  </si>
+  <si>
+    <t>刀剑训练</t>
+  </si>
+  <si>
+    <t>毁灭训练</t>
+  </si>
+  <si>
+    <t>力量共享</t>
+  </si>
+  <si>
+    <t>寒冰共享</t>
+  </si>
+  <si>
+    <t>烈焰共享</t>
+  </si>
+  <si>
+    <t>雷霆共享</t>
+  </si>
+  <si>
+    <t>混乱共享</t>
+  </si>
+  <si>
+    <t>精密器械</t>
+  </si>
+  <si>
+    <t>加强弹簧</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>1083</t>
+  </si>
+  <si>
+    <t>1084</t>
+  </si>
+  <si>
+    <t>1085</t>
+  </si>
+  <si>
+    <t>1086</t>
+  </si>
+  <si>
+    <t>1087</t>
+  </si>
+  <si>
+    <t>1088</t>
+  </si>
+  <si>
+    <t>1089</t>
+  </si>
+  <si>
+    <t>1090</t>
+  </si>
+  <si>
+    <t>1091</t>
+  </si>
+  <si>
+    <t>1092</t>
+  </si>
+  <si>
+    <t>1093</t>
+  </si>
+  <si>
+    <t>1094</t>
+  </si>
+  <si>
+    <t>1095</t>
+  </si>
+  <si>
+    <t>诅咒持续时间+2秒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>诅咒范围+30%</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>诅咒技能冷却时间减少10%</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放诅咒恢复自身1%生命值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤物发射投射物数量+2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤物近战技能范围+30%</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤物区域技能范围+30%</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤物和陷阱继承100%角色物理伤害加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤物和陷阱继承100%角色冰霜伤害加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤物和陷阱继承100%角色火焰伤害加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤物和陷阱继承100%角色闪电伤害加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤物和陷阱继承100%角色混沌伤害加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陷阱发射投射物数量+2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陷阱区域技能范围+30%</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>诅咒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤物
+陷阱</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -5525,7 +5661,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -5536,8 +5672,9 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5637,14 +5774,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="差" xfId="2" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2 20" xfId="4" xr:uid="{091FF147-A38D-473E-82F8-F2F0D8E876D5}"/>
     <cellStyle name="好" xfId="1" builtinId="26"/>
     <cellStyle name="适中" xfId="3" builtinId="28"/>
   </cellStyles>
   <dxfs count="50">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5824,70 +6033,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="right"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center"/>
@@ -6250,52 +6395,52 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="表3" displayName="表3" ref="C8:R159" tableType="xml" totalsRowShown="0" connectionId="24">
   <autoFilter ref="C8:R159" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" uniqueName="id_i" name="id_i" dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" uniqueName="id_i" name="id_i" dataDxfId="16">
       <xmlColumnPr mapId="48" xpath="/root/data/id_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" uniqueName="type_i" name="type_i" dataDxfId="33">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" uniqueName="type_i" name="type_i" dataDxfId="15">
       <xmlColumnPr mapId="48" xpath="/root/data/type_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8F6BE4E5-DA90-43FC-B30A-9A749659FC4C}" uniqueName="spell_limit_i" name="spell_limit_i" dataDxfId="32">
+    <tableColumn id="2" xr3:uid="{8F6BE4E5-DA90-43FC-B30A-9A749659FC4C}" uniqueName="spell_limit_i" name="spell_limit_i" dataDxfId="14">
       <xmlColumnPr mapId="48" xpath="/root/data/spell_limit_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" uniqueName="bd1_i" name="bd1_i" dataDxfId="31">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" uniqueName="bd1_i" name="bd1_i" dataDxfId="13">
       <xmlColumnPr mapId="48" xpath="/root/data/bd1_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" uniqueName="bd2_i" name="bd2_i" dataDxfId="30">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" uniqueName="bd2_i" name="bd2_i" dataDxfId="12">
       <xmlColumnPr mapId="48" xpath="/root/data/bd2_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" uniqueName="bd3_i" name="bd3_i" dataDxfId="29">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" uniqueName="bd3_i" name="bd3_i" dataDxfId="11">
       <xmlColumnPr mapId="48" xpath="/root/data/bd3_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" uniqueName="bd4_i" name="bd4_i" dataDxfId="28">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" uniqueName="bd4_i" name="bd4_i" dataDxfId="10">
       <xmlColumnPr mapId="48" xpath="/root/data/bd4_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" uniqueName="vocation1_i" name="vocation1_i" dataDxfId="27">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" uniqueName="vocation1_i" name="vocation1_i" dataDxfId="9">
       <xmlColumnPr mapId="48" xpath="/root/data/vocation1_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" uniqueName="vocation2_i" name="vocation2_i" dataDxfId="26">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" uniqueName="vocation2_i" name="vocation2_i" dataDxfId="8">
       <xmlColumnPr mapId="48" xpath="/root/data/vocation2_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" uniqueName="vocation3_i" name="vocation3_i" dataDxfId="25">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" uniqueName="vocation3_i" name="vocation3_i" dataDxfId="7">
       <xmlColumnPr mapId="48" xpath="/root/data/vocation3_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" uniqueName="vocation4_i" name="vocation4_i" dataDxfId="24">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" uniqueName="vocation4_i" name="vocation4_i" dataDxfId="6">
       <xmlColumnPr mapId="48" xpath="/root/data/vocation4_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" uniqueName="vocation5_i" name="vocation5_i" dataDxfId="23">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" uniqueName="vocation5_i" name="vocation5_i" dataDxfId="5">
       <xmlColumnPr mapId="48" xpath="/root/data/vocation5_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" uniqueName="vocation6_i" name="vocation6_i" dataDxfId="22">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" uniqueName="vocation6_i" name="vocation6_i" dataDxfId="4">
       <xmlColumnPr mapId="48" xpath="/root/data/vocation6_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" uniqueName="vocation7_i" name="vocation7_i" dataDxfId="21">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" uniqueName="vocation7_i" name="vocation7_i" dataDxfId="3">
       <xmlColumnPr mapId="48" xpath="/root/data/vocation7_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" uniqueName="vocation8_i" name="vocation8_i" dataDxfId="20">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" uniqueName="vocation8_i" name="vocation8_i" dataDxfId="2">
       <xmlColumnPr mapId="48" xpath="/root/data/vocation8_i" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{8A8D575D-CD28-46B2-9A33-80365C57DA85}" uniqueName="bd_exclusion_l" name="bd_exclusion_l" dataDxfId="19">
+    <tableColumn id="16" xr3:uid="{8A8D575D-CD28-46B2-9A33-80365C57DA85}" uniqueName="bd_exclusion_l" name="bd_exclusion_l" dataDxfId="1">
       <xmlColumnPr mapId="48" xpath="/root/data/bd_exclusion_l" xmlDataType="integer"/>
     </tableColumn>
   </tableColumns>
@@ -6331,10 +6476,10 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="表4" displayName="表4" ref="D6:H88" tableType="xml" totalsRowShown="0" connectionId="16">
-  <autoFilter ref="D6:H88" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="表4" displayName="表4" ref="D6:H102" tableType="xml" totalsRowShown="0" connectionId="16">
+  <autoFilter ref="D6:H102" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" uniqueName="id_i" name="id_i" dataDxfId="18">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" uniqueName="id_i" name="id_i" dataDxfId="0">
       <xmlColumnPr mapId="49" xpath="/root/data/id_i" xmlDataType="integer"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" uniqueName="param_type_i" name="param_type_i">
@@ -23906,34 +24051,34 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="C25:C30">
-    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C122">
-    <cfRule type="duplicateValues" dxfId="12" priority="193"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C123:C125">
-    <cfRule type="duplicateValues" dxfId="9" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C126:C138">
-    <cfRule type="duplicateValues" dxfId="7" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C139">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C140:C149">
-    <cfRule type="duplicateValues" dxfId="2" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="202"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -25204,7 +25349,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.875" customWidth="1"/>
@@ -27258,8 +27403,353 @@
         <v>1450</v>
       </c>
     </row>
+    <row r="89" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B89" s="42" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C89" s="41" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>1655</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>100</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B90" s="42"/>
+      <c r="C90" s="41" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>100</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B91" s="42"/>
+      <c r="C91" s="41" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>100</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B92" s="42"/>
+      <c r="C92" s="41" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92">
+        <v>100</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B93" s="43" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C93" s="41" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93">
+        <v>100</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B94" s="42"/>
+      <c r="C94" s="41" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94">
+        <v>100</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B95" s="42"/>
+      <c r="C95" s="41" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95">
+        <v>100</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B96" s="42"/>
+      <c r="C96" s="41" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96">
+        <v>100</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B97" s="42"/>
+      <c r="C97" s="41" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>1663</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
+        <v>100</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B98" s="42"/>
+      <c r="C98" s="41" t="s">
+        <v>1678</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>1664</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
+        <v>100</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B99" s="42"/>
+      <c r="C99" s="41" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>100</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B100" s="42"/>
+      <c r="C100" s="41" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100">
+        <v>100</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B101" s="42" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C101" s="41" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>100</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B102" s="42"/>
+      <c r="C102" s="41" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102">
+        <v>100</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>1668</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="17">
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="B93:B100"/>
+    <mergeCell ref="B89:B92"/>
     <mergeCell ref="B48:B52"/>
     <mergeCell ref="B8:B20"/>
     <mergeCell ref="B21:B24"/>
